--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487088_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487088_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4087</v>
+        <v>8.274800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3003</v>
+        <v>3.0593</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1084</v>
+        <v>5.2155</v>
       </c>
       <c r="G2" t="n">
         <v>6.0212</v>
@@ -610,13 +610,13 @@
         <v>3.4741</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1216</v>
+        <v>-0.2555</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5671</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4455</v>
+        <v>0.5525</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7199</v>
+        <v>7.7338</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1083</v>
+        <v>6.908</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6116</v>
+        <v>0.8258</v>
       </c>
       <c r="G3" t="n">
         <v>4.0285</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1124</v>
+        <v>0.1262</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3702</v>
+        <v>0.1699</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2578</v>
+        <v>-0.0436</v>
       </c>
       <c r="V3" t="n">
         <v>1.842</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.2023</v>
+        <v>7.0301</v>
       </c>
       <c r="E4" t="n">
-        <v>3.483</v>
+        <v>4.4713</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7193</v>
+        <v>2.5588</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1474</v>
+        <v>6.7206</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6608</v>
+        <v>3.5739</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4866</v>
+        <v>3.1467</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2472</v>
+        <v>6.333</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7413</v>
+        <v>3.167</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5059</v>
+        <v>3.166</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0998</v>
+        <v>0.3876</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0805</v>
+        <v>0.4069</v>
       </c>
       <c r="O4" t="n">
         <v>-0.0193</v>
       </c>
       <c r="P4" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
         <v>2.8951</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4759</v>
+        <v>-0.1068</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4481</v>
+        <v>-0.8966</v>
       </c>
       <c r="U4" t="n">
-        <v>0.924</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.614</v>
+        <v>-1.5138</v>
       </c>
       <c r="W4" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>7.1976</v>
+        <v>6.8345</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3712</v>
+        <v>3.3828</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8265</v>
+        <v>3.4516</v>
       </c>
       <c r="G5" t="n">
-        <v>6.7206</v>
+        <v>5.1474</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5739</v>
+        <v>3.6608</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1467</v>
+        <v>1.4866</v>
       </c>
       <c r="J5" t="n">
-        <v>6.333</v>
+        <v>5.2472</v>
       </c>
       <c r="K5" t="n">
-        <v>3.167</v>
+        <v>3.7413</v>
       </c>
       <c r="L5" t="n">
-        <v>3.166</v>
+        <v>1.5059</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3876</v>
+        <v>-0.0998</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4069</v>
+        <v>-0.0805</v>
       </c>
       <c r="O5" t="n">
         <v>-0.0193</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
         <v>2.8951</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0608</v>
+        <v>0.1081</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9967</v>
+        <v>-0.5483</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0575</v>
+        <v>0.6563</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5138</v>
+        <v>0.614</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6.9411</v>
+        <v>6.4126</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6769</v>
+        <v>4.3358</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2642</v>
+        <v>2.0768</v>
       </c>
       <c r="G6" t="n">
         <v>3.4321</v>
@@ -922,13 +922,13 @@
         <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>0.544</v>
+        <v>0.0155</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3107</v>
+        <v>-0.0304</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2333</v>
+        <v>0.0459</v>
       </c>
       <c r="V6" t="n">
         <v>1.228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8227</v>
+        <v>3.2292</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6157</v>
+        <v>2.0757</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2071</v>
+        <v>1.1535</v>
       </c>
       <c r="G7" t="n">
         <v>2.5364</v>
@@ -1000,13 +1000,13 @@
         <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2578</v>
+        <v>0.1487</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4164</v>
+        <v>0.0436</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1586</v>
+        <v>0.1051</v>
       </c>
       <c r="V7" t="n">
         <v>-0.614</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7468</v>
+        <v>1.9272</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.778</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5248</v>
+        <v>2.6051</v>
       </c>
       <c r="G8" t="n">
         <v>0.4017</v>
@@ -1078,13 +1078,13 @@
         <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.392</v>
+        <v>-0.2115</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7588</v>
+        <v>-0.6587</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3668</v>
+        <v>0.4471</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.221</v>
+        <v>0.2478</v>
       </c>
       <c r="E9" t="n">
         <v>0.5046</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2836</v>
+        <v>-0.2568</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0044</v>
@@ -1156,13 +1156,13 @@
         <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1606</v>
+        <v>-0.1338</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6372</v>
+        <v>-0.7849</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.7961</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1183</v>
+        <v>0.0112</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0113</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3741</v>
+        <v>0.2264</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2512</v>
+        <v>0.2105</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1229</v>
+        <v>0.0159</v>
       </c>
       <c r="V10" t="n">
         <v>-0.614</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1203</v>
+        <v>-0.9071</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2377</v>
+        <v>-1.0781</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1174</v>
+        <v>0.1709</v>
       </c>
       <c r="G11" t="n">
         <v>-2.015</v>
@@ -1312,13 +1312,13 @@
         <v>1.7371</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5142</v>
+        <v>-0.3011</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4164</v>
+        <v>-0.2568</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0978</v>
+        <v>-0.0443</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3281</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8423</v>
+        <v>-2.0402</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.4394</v>
+        <v>-5.0389</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5971</v>
+        <v>2.9987</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0274</v>
@@ -1390,13 +1390,13 @@
         <v>1.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1587</v>
+        <v>-0.3566</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8778</v>
+        <v>-0.4772</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2809</v>
+        <v>0.1206</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6562</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>37.6603</v>
+        <v>37.9578</v>
       </c>
       <c r="E13" t="n">
-        <v>16.8494</v>
+        <v>17.1465</v>
       </c>
       <c r="F13" t="n">
         <v>20.8111</v>
@@ -1468,10 +1468,10 @@
         <v>22.196</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0377</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7277</v>
+        <v>-3.4305</v>
       </c>
       <c r="U13" t="n">
         <v>2.6899</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1443</v>
+        <v>-0.064</v>
       </c>
       <c r="E14" t="n">
         <v>0.0226</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1669</v>
+        <v>-0.0866</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1383</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0059</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0535</v>
+        <v>0.1338</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.1478</v>
+        <v>-1.7869</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8253</v>
+        <v>-0.625</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3225</v>
+        <v>-1.1619</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7749</v>
@@ -1624,13 +1624,13 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6359</v>
+        <v>-0.275</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5658</v>
+        <v>-0.3655</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0701</v>
+        <v>0.0905</v>
       </c>
       <c r="V15" t="n">
         <v>0.614</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ALLAS MENESES</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.4313</v>
+        <v>-3.4484</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1261</v>
+        <v>-1.0262</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3052</v>
+        <v>-2.4222</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8735</v>
+        <v>-1.0443</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0938</v>
+        <v>-0.2225</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.8219</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5907</v>
+        <v>2.3995</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6314</v>
+        <v>3.0428</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0407</v>
+        <v>-0.6433</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2828</v>
+        <v>-3.4438</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4624</v>
+        <v>-3.2652</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8204</v>
+        <v>-0.1785</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.579</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R16" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6352</v>
+        <v>-0.1229</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4297</v>
+        <v>-0.7935</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2056</v>
+        <v>0.6705</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.614</v>
+        <v>0.614</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X16" t="n">
         <v>-0.614</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. SANCHEZ TURRION</t>
+          <t>D. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.17</v>
+        <v>-3.6584</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3617</v>
+        <v>-1.3264</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8083</v>
+        <v>-2.332</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0875</v>
+        <v>-2.8735</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8547</v>
+        <v>-2.0938</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2328</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5534</v>
+        <v>-0.5907</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2588</v>
+        <v>-0.6314</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2945</v>
+        <v>0.0407</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5341</v>
+        <v>-2.2828</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5959</v>
+        <v>-1.4624</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0617</v>
+        <v>-0.8204</v>
       </c>
       <c r="P17" t="n">
-        <v>0.193</v>
+        <v>-0.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1805</v>
+        <v>0.4082</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1917</v>
+        <v>0.2294</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0112</v>
+        <v>0.1788</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.4559</v>
+        <v>-0.614</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4559</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>L. SANCHEZ TURRION</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.2351</v>
+        <v>-4.1759</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9889</v>
+        <v>-1.6621</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2463</v>
+        <v>-2.5139</v>
       </c>
       <c r="G18" t="n">
-        <v>-6.4218</v>
+        <v>-2.0875</v>
       </c>
       <c r="H18" t="n">
-        <v>-7.2836</v>
+        <v>-1.8547</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8618</v>
+        <v>-0.2328</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0492</v>
+        <v>-1.5534</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.0434</v>
+        <v>-0.2588</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9943</v>
+        <v>-1.2945</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.3726</v>
+        <v>-0.5341</v>
       </c>
       <c r="N18" t="n">
-        <v>-4.2401</v>
+        <v>-1.5959</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1325</v>
+        <v>1.0617</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.158</v>
+        <v>0.193</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7886</v>
+        <v>0.1745</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0556</v>
+        <v>-0.1087</v>
       </c>
       <c r="U18" t="n">
-        <v>1.733</v>
+        <v>0.2832</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5561</v>
+        <v>-2.4559</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6562</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.27</v>
+        <v>-4.5547</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5269</v>
+        <v>-3.4368</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.7431</v>
+        <v>-1.1179</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0443</v>
+        <v>-1.8916</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2225</v>
+        <v>-2.4778</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8219</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3995</v>
+        <v>1.9324</v>
       </c>
       <c r="K19" t="n">
-        <v>3.0428</v>
+        <v>0.093</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6433</v>
+        <v>1.8393</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.4438</v>
+        <v>-3.8239</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.2652</v>
+        <v>-2.5708</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1785</v>
+        <v>-1.2531</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.8951</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8602</v>
+        <v>-4.8252</v>
       </c>
       <c r="R19" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9445</v>
+        <v>0.2898</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2942</v>
+        <v>-0.544</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3496</v>
+        <v>0.8338</v>
       </c>
       <c r="V19" t="n">
-        <v>0.614</v>
+        <v>0.3281</v>
       </c>
       <c r="W19" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.614</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>S. MARTINEZ ORTIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3799</v>
+        <v>-5.1627</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6371</v>
+        <v>-4.9151</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7428</v>
+        <v>-0.2476</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8916</v>
+        <v>-2.3677</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4778</v>
+        <v>-2.604</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.2363</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9324</v>
+        <v>-0.4994</v>
       </c>
       <c r="K20" t="n">
-        <v>0.093</v>
+        <v>-0.5072</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8393</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.8239</v>
+        <v>-1.8683</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.5708</v>
+        <v>-2.0968</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2531</v>
+        <v>0.2285</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.2811</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.8252</v>
+        <v>-3.8602</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4647</v>
+        <v>-0.0929</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7442</v>
+        <v>-0.5555</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2089</v>
+        <v>0.4627</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MARTINEZ ORTIZ</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.904</v>
+        <v>-5.2517</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.4158</v>
+        <v>-3.3894</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4882</v>
+        <v>-1.8623</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3677</v>
+        <v>-6.4218</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.604</v>
+        <v>-7.2836</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2363</v>
+        <v>0.8618</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4994</v>
+        <v>-1.0492</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5072</v>
+        <v>-3.0434</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.9943</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8683</v>
+        <v>-5.3726</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0968</v>
+        <v>-4.2401</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2285</v>
+        <v>-1.1325</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.7021</v>
+        <v>-1.158</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.8602</v>
+        <v>-2.8951</v>
       </c>
       <c r="R21" t="n">
-        <v>1.158</v>
+        <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8342000000000001</v>
+        <v>0.772</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0562</v>
+        <v>-0.345</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2221</v>
+        <v>1.117</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.5561</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.9779</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.952</v>
+        <v>-4.4527</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.026</v>
+        <v>-4.4374</v>
       </c>
       <c r="G22" t="n">
         <v>-7.6302</v>
@@ -2170,13 +2170,13 @@
         <v>1.158</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3894</v>
+        <v>0.4773</v>
       </c>
       <c r="T22" t="n">
-        <v>0.353</v>
+        <v>-0.1477</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0363</v>
+        <v>0.6249</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-37.6603</v>
+        <v>-36.9927</v>
       </c>
       <c r="E23" t="n">
-        <v>-20.8112</v>
+        <v>-20.8111</v>
       </c>
       <c r="F23" t="n">
-        <v>-16.8493</v>
+        <v>-16.1818</v>
       </c>
       <c r="G23" t="n">
         <v>-25.2298</v>
@@ -2218,16 +2218,16 @@
         <v>-21.0313</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.1985</v>
+        <v>-4.198499999999999</v>
       </c>
       <c r="J23" t="n">
         <v>1.333</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2046</v>
+        <v>1.204600000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1286999999999998</v>
+        <v>0.1286999999999996</v>
       </c>
       <c r="M23" t="n">
         <v>-26.5628</v>
@@ -2248,16 +2248,16 @@
         <v>8.6853</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0379</v>
+        <v>1.7054</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.6899</v>
+        <v>-2.69</v>
       </c>
       <c r="U23" t="n">
-        <v>3.7277</v>
+        <v>4.3952</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0423</v>
+        <v>0.04229999999999989</v>
       </c>
       <c r="W23" t="n">
         <v>2.7419</v>
